--- a/DataVaryingTemperature/LSR_20251119_all_materials_2.xlsx
+++ b/DataVaryingTemperature/LSR_20251119_all_materials_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Personal\suresh\Software\Github\ERSL-Private\METALS\DataVaryingTemperature\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52BC539D-6347-489E-B814-97B7C5EB86BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E927CEA-6288-47CD-BB79-9833F4DCF5B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -218,7 +218,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -240,12 +240,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -277,7 +271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -328,12 +322,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -754,25 +742,25 @@
       <c r="D3" s="17">
         <v>31660210473.422401</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="12">
         <f>D3*EXP(-2000/Q3)</f>
         <v>318975670.52076489</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="12">
         <f>0.1*D3*EXP(-3000/Q3)</f>
         <v>3201691.1808246872</v>
       </c>
-      <c r="G3" s="17">
+      <c r="G3" s="12">
         <v>1.0001904096107801</v>
       </c>
-      <c r="H3" s="17">
+      <c r="H3" s="12">
         <v>168216570.304768</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="12">
         <f>0.1*H3*EXP(-2000/Q3)</f>
         <v>169477.68982998349</v>
       </c>
-      <c r="J3" s="18">
+      <c r="J3" s="12">
         <f>0.1*H3*EXP(-3000/Q3)</f>
         <v>17011.179065454031</v>
       </c>
@@ -794,7 +782,7 @@
       <c r="P3" s="15">
         <v>0.25</v>
       </c>
-      <c r="Q3" s="19">
+      <c r="Q3" s="12">
         <v>435</v>
       </c>
       <c r="R3" s="8">
@@ -814,11 +802,11 @@
       <c r="D4" s="12">
         <v>88122361302.941193</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="12">
         <f t="shared" ref="E4:E5" si="0">D4*EXP(-2000/Q4)</f>
         <v>425450353.708947</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="12">
         <f t="shared" ref="F4:F5" si="1">0.1*D4*EXP(-3000/Q4)</f>
         <v>2956175.8899659268</v>
       </c>
@@ -828,11 +816,11 @@
       <c r="H4" s="12">
         <v>331895501.95574099</v>
       </c>
-      <c r="I4" s="18">
+      <c r="I4" s="12">
         <f t="shared" ref="I4:I5" si="2">0.1*H4*EXP(-2000/Q4)</f>
         <v>160237.4886619903</v>
       </c>
-      <c r="J4" s="18">
+      <c r="J4" s="12">
         <f t="shared" ref="J4:J5" si="3">0.1*H4*EXP(-3000/Q4)</f>
         <v>11133.853727509615</v>
       </c>
@@ -854,7 +842,7 @@
       <c r="P4" s="15">
         <v>0.74</v>
       </c>
-      <c r="Q4" s="19">
+      <c r="Q4" s="12">
         <v>375</v>
       </c>
       <c r="R4" s="8">
@@ -874,11 +862,11 @@
       <c r="D5" s="12">
         <v>92976880986.810806</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="12">
         <f t="shared" si="0"/>
         <v>306684777.10425931</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="12">
         <f t="shared" si="1"/>
         <v>1761371.0038603023</v>
       </c>
@@ -888,11 +876,11 @@
       <c r="H5" s="12">
         <v>413532439.30818099</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="12">
         <f t="shared" si="2"/>
         <v>136403.9131325568</v>
       </c>
-      <c r="J5" s="18">
+      <c r="J5" s="12">
         <f t="shared" si="3"/>
         <v>7834.0340095552874</v>
       </c>
@@ -914,7 +902,7 @@
       <c r="P5" s="15">
         <v>0.15</v>
       </c>
-      <c r="Q5" s="19">
+      <c r="Q5" s="12">
         <v>350</v>
       </c>
       <c r="R5" s="8">
@@ -970,7 +958,7 @@
       <c r="P6" s="15">
         <v>0.46</v>
       </c>
-      <c r="Q6" s="19">
+      <c r="Q6" s="12">
         <v>1050</v>
       </c>
       <c r="R6" s="8">
@@ -1028,7 +1016,7 @@
       <c r="P7" s="15">
         <v>0.41</v>
       </c>
-      <c r="Q7" s="19">
+      <c r="Q7" s="12">
         <v>1050</v>
       </c>
       <c r="R7" s="8">
@@ -1084,7 +1072,7 @@
       <c r="P8" s="15">
         <v>0.36</v>
       </c>
-      <c r="Q8" s="19">
+      <c r="Q8" s="12">
         <v>1050</v>
       </c>
       <c r="R8" s="8">
@@ -1140,7 +1128,7 @@
       <c r="P9" s="15">
         <v>0.35</v>
       </c>
-      <c r="Q9" s="19">
+      <c r="Q9" s="12">
         <v>1040</v>
       </c>
       <c r="R9" s="8">
@@ -1196,7 +1184,7 @@
       <c r="P10" s="15">
         <v>0.64</v>
       </c>
-      <c r="Q10" s="19">
+      <c r="Q10" s="12">
         <v>1000</v>
       </c>
       <c r="R10" s="8">
@@ -1252,7 +1240,7 @@
       <c r="P11" s="15">
         <v>1E-3</v>
       </c>
-      <c r="Q11" s="19">
+      <c r="Q11" s="12">
         <v>1200</v>
       </c>
       <c r="R11" s="8">
@@ -1308,7 +1296,7 @@
       <c r="P12" s="15">
         <v>1E-3</v>
       </c>
-      <c r="Q12" s="19">
+      <c r="Q12" s="12">
         <v>1200</v>
       </c>
       <c r="R12" s="8">
